--- a/画面設計.xlsx
+++ b/画面設計.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\大熊 翔\Documents\develop\PC台帳管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\大熊 翔\Documents\develop\it-asset-manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34C77F0-47B5-4DF9-9597-A9477E54D065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC28EB6-5E88-430D-A53E-1A0B171B33CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ED5045D5-42AE-432F-9376-EB2648F4B0FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ED5045D5-42AE-432F-9376-EB2648F4B0FA}"/>
   </bookViews>
   <sheets>
     <sheet name="改版履歴" sheetId="2" r:id="rId1"/>
@@ -3393,8 +3393,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14030823" y="3723867"/>
-          <a:ext cx="635454" cy="931000"/>
+          <a:off x="14028918" y="3706722"/>
+          <a:ext cx="633549" cy="931000"/>
           <a:chOff x="11107615" y="3687288"/>
           <a:chExt cx="661741" cy="1078143"/>
         </a:xfrm>
@@ -6442,7 +6442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA184F7-3BA9-4E95-829F-1E5C5468CA7A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6452,26 +6452,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81987455-16C5-4B2D-A160-84402631C0ED}">
   <dimension ref="A1:CX69"/>
-  <sheetFormatPr defaultColWidth="1.69921875" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="1.75" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="1.69921875" customWidth="1"/>
-    <col min="4" max="4" width="1.69921875" style="18"/>
-    <col min="5" max="5" width="1.69921875" customWidth="1"/>
+    <col min="2" max="2" width="1.75" customWidth="1"/>
+    <col min="4" max="4" width="1.75" style="18"/>
+    <col min="5" max="5" width="1.75" customWidth="1"/>
     <col min="6" max="6" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="1.69921875" customWidth="1"/>
-    <col min="24" max="24" width="1.69921875" customWidth="1"/>
-    <col min="30" max="30" width="1.69921875" customWidth="1"/>
-    <col min="34" max="34" width="1.69921875" customWidth="1"/>
-    <col min="43" max="44" width="1.69921875" customWidth="1"/>
-    <col min="49" max="49" width="1.69921875" style="18"/>
-    <col min="54" max="54" width="1.69921875" style="18"/>
-    <col min="61" max="62" width="1.69921875" customWidth="1"/>
-    <col min="93" max="95" width="1.69921875" customWidth="1"/>
-    <col min="97" max="99" width="2.19921875" customWidth="1"/>
+    <col min="20" max="20" width="1.75" customWidth="1"/>
+    <col min="24" max="24" width="1.75" customWidth="1"/>
+    <col min="30" max="30" width="1.75" customWidth="1"/>
+    <col min="34" max="34" width="1.75" customWidth="1"/>
+    <col min="43" max="44" width="1.75" customWidth="1"/>
+    <col min="49" max="49" width="1.75" style="18"/>
+    <col min="54" max="54" width="1.75" style="18"/>
+    <col min="61" max="62" width="1.75" customWidth="1"/>
+    <col min="93" max="95" width="1.75" customWidth="1"/>
+    <col min="97" max="99" width="2.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:102" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:102" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="13" t="s">
         <v>5</v>
       </c>
@@ -6511,8 +6511,8 @@
       </c>
       <c r="AA2" s="12"/>
     </row>
-    <row r="3" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:102" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:102" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -6617,8 +6617,8 @@
       <c r="CW4" s="9"/>
       <c r="CX4" s="9"/>
     </row>
-    <row r="5" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="6" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6697,7 +6697,7 @@
       <c r="BX6" s="2"/>
       <c r="BY6" s="2"/>
     </row>
-    <row r="7" spans="1:102" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:102" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="74" t="s">
@@ -6777,7 +6777,7 @@
       <c r="BX7" s="2"/>
       <c r="BY7" s="2"/>
     </row>
-    <row r="8" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6856,7 +6856,7 @@
       <c r="BX8" s="2"/>
       <c r="BY8" s="2"/>
     </row>
-    <row r="9" spans="1:102" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:102" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6961,7 +6961,7 @@
       <c r="CV9" s="2"/>
       <c r="CW9" s="2"/>
     </row>
-    <row r="10" spans="1:102" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:102" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7063,7 +7063,7 @@
       <c r="CV10" s="2"/>
       <c r="CW10" s="2"/>
     </row>
-    <row r="11" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7126,7 +7126,7 @@
       <c r="CV11" s="2"/>
       <c r="CW11" s="2"/>
     </row>
-    <row r="12" spans="1:102" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:102" ht="12.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7200,7 +7200,7 @@
       <c r="CV12" s="2"/>
       <c r="CW12" s="2"/>
     </row>
-    <row r="13" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -7265,7 +7265,7 @@
       <c r="CV13" s="2"/>
       <c r="CW13" s="2"/>
     </row>
-    <row r="14" spans="1:102" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:102" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7330,7 +7330,7 @@
       <c r="CV14" s="2"/>
       <c r="CW14" s="2"/>
     </row>
-    <row r="15" spans="1:102" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:102" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7395,7 +7395,7 @@
       <c r="CV15" s="2"/>
       <c r="CW15" s="2"/>
     </row>
-    <row r="16" spans="1:102" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:102" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7461,7 +7461,7 @@
       <c r="CV16" s="2"/>
       <c r="CW16" s="2"/>
     </row>
-    <row r="17" spans="1:99" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:99" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7503,7 +7503,7 @@
       <c r="BX17" s="2"/>
       <c r="BY17" s="2"/>
     </row>
-    <row r="18" spans="1:99" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:99" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7583,7 +7583,7 @@
       <c r="BY18" s="2"/>
       <c r="CS18" s="2"/>
     </row>
-    <row r="19" spans="1:99" s="18" customFormat="1" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:99" s="18" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7663,7 +7663,7 @@
       <c r="BY19" s="2"/>
       <c r="CS19" s="2"/>
     </row>
-    <row r="20" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -7742,7 +7742,7 @@
       <c r="BX20" s="2"/>
       <c r="BY20" s="2"/>
     </row>
-    <row r="21" spans="1:99" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:99" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="56" t="s">
@@ -7915,7 +7915,7 @@
       <c r="CT21" s="60"/>
       <c r="CU21" s="57"/>
     </row>
-    <row r="22" spans="1:99" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:99" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="43" t="s">
@@ -8060,7 +8060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:99" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:99" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="43" t="s">
@@ -8205,13 +8205,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -8290,7 +8290,7 @@
       <c r="BX25" s="2"/>
       <c r="BY25" s="2"/>
     </row>
-    <row r="26" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -8369,7 +8369,7 @@
       <c r="BX26" s="2"/>
       <c r="BY26" s="2"/>
     </row>
-    <row r="27" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -8448,10 +8448,10 @@
       <c r="BX27" s="2"/>
       <c r="BY27" s="2"/>
     </row>
-    <row r="28" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BY28" s="2"/>
     </row>
-    <row r="29" spans="1:99" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:99" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="8" t="s">
         <v>15</v>
       </c>
@@ -8510,8 +8510,8 @@
       <c r="BC29" s="9"/>
       <c r="BD29" s="9"/>
     </row>
-    <row r="30" spans="1:99" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="31" spans="1:99" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:99" ht="10.15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:99" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="77" t="s">
         <v>20</v>
       </c>
@@ -8575,7 +8575,7 @@
       <c r="AV31" s="25"/>
       <c r="AW31" s="78"/>
     </row>
-    <row r="32" spans="1:99" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:99" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="76">
         <v>1</v>
       </c>
@@ -8629,7 +8629,7 @@
       <c r="AV32" s="99"/>
       <c r="AW32" s="99"/>
     </row>
-    <row r="33" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="29"/>
       <c r="C33" s="27"/>
       <c r="D33" s="42">
@@ -8692,7 +8692,7 @@
       <c r="AV33" s="16"/>
       <c r="AW33" s="17"/>
     </row>
-    <row r="34" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="76">
         <v>2</v>
       </c>
@@ -8746,7 +8746,7 @@
       <c r="AV34" s="99"/>
       <c r="AW34" s="99"/>
     </row>
-    <row r="35" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="30"/>
       <c r="C35" s="31"/>
       <c r="D35" s="42">
@@ -8810,7 +8810,7 @@
       <c r="AV35" s="16"/>
       <c r="AW35" s="17"/>
     </row>
-    <row r="36" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="30"/>
       <c r="C36" s="31"/>
       <c r="D36" s="42">
@@ -8872,7 +8872,7 @@
       <c r="AV36" s="16"/>
       <c r="AW36" s="17"/>
     </row>
-    <row r="37" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="30"/>
       <c r="C37" s="31"/>
       <c r="D37" s="42">
@@ -8934,7 +8934,7 @@
       <c r="AV37" s="16"/>
       <c r="AW37" s="17"/>
     </row>
-    <row r="38" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="84"/>
       <c r="C38" s="31"/>
       <c r="D38" s="42">
@@ -8998,7 +8998,7 @@
       <c r="AV38" s="16"/>
       <c r="AW38" s="17"/>
     </row>
-    <row r="39" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="29"/>
       <c r="C39" s="27"/>
       <c r="D39" s="42">
@@ -9062,7 +9062,7 @@
       <c r="AV39" s="16"/>
       <c r="AW39" s="17"/>
     </row>
-    <row r="40" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="76">
         <v>3</v>
       </c>
@@ -9116,7 +9116,7 @@
       <c r="AV40" s="99"/>
       <c r="AW40" s="99"/>
     </row>
-    <row r="41" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="30"/>
       <c r="C41" s="31"/>
       <c r="D41" s="42">
@@ -9180,7 +9180,7 @@
       <c r="AV41" s="16"/>
       <c r="AW41" s="17"/>
     </row>
-    <row r="42" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="30"/>
       <c r="C42" s="31"/>
       <c r="D42" s="42">
@@ -9244,7 +9244,7 @@
       <c r="AV42" s="16"/>
       <c r="AW42" s="17"/>
     </row>
-    <row r="43" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="30"/>
       <c r="C43" s="32"/>
       <c r="D43" s="42">
@@ -9308,7 +9308,7 @@
       <c r="AV43" s="16"/>
       <c r="AW43" s="17"/>
     </row>
-    <row r="44" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="30"/>
       <c r="C44" s="32"/>
       <c r="D44" s="42">
@@ -9372,7 +9372,7 @@
       <c r="AV44" s="16"/>
       <c r="AW44" s="17"/>
     </row>
-    <row r="45" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:49" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="29"/>
       <c r="C45" s="72"/>
       <c r="D45" s="42">
@@ -9436,7 +9436,7 @@
       <c r="AV45" s="16"/>
       <c r="AW45" s="17"/>
     </row>
-    <row r="46" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="76">
         <v>4</v>
       </c>
@@ -9490,7 +9490,7 @@
       <c r="AV46" s="99"/>
       <c r="AW46" s="99"/>
     </row>
-    <row r="47" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="30"/>
       <c r="C47" s="37"/>
       <c r="D47" s="42">
@@ -9552,7 +9552,7 @@
       <c r="AV47" s="16"/>
       <c r="AW47" s="17"/>
     </row>
-    <row r="48" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="30"/>
       <c r="C48" s="37"/>
       <c r="D48" s="42">
@@ -9614,7 +9614,7 @@
       <c r="AV48" s="16"/>
       <c r="AW48" s="17"/>
     </row>
-    <row r="49" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="30"/>
       <c r="C49" s="37"/>
       <c r="D49" s="42">
@@ -9676,7 +9676,7 @@
       <c r="AV49" s="16"/>
       <c r="AW49" s="17"/>
     </row>
-    <row r="50" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="30"/>
       <c r="C50" s="37"/>
       <c r="D50" s="42">
@@ -9738,7 +9738,7 @@
       <c r="AV50" s="16"/>
       <c r="AW50" s="17"/>
     </row>
-    <row r="51" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="30"/>
       <c r="C51" s="37"/>
       <c r="D51" s="42">
@@ -9800,7 +9800,7 @@
       <c r="AV51" s="16"/>
       <c r="AW51" s="17"/>
     </row>
-    <row r="52" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="30"/>
       <c r="C52" s="37"/>
       <c r="D52" s="42">
@@ -9862,7 +9862,7 @@
       <c r="AV52" s="16"/>
       <c r="AW52" s="17"/>
     </row>
-    <row r="53" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="30"/>
       <c r="C53" s="37"/>
       <c r="D53" s="42">
@@ -9924,7 +9924,7 @@
       <c r="AV53" s="16"/>
       <c r="AW53" s="17"/>
     </row>
-    <row r="54" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="30"/>
       <c r="C54" s="37"/>
       <c r="D54" s="42">
@@ -9986,7 +9986,7 @@
       <c r="AV54" s="16"/>
       <c r="AW54" s="17"/>
     </row>
-    <row r="55" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="30"/>
       <c r="C55" s="37"/>
       <c r="D55" s="42">
@@ -10048,7 +10048,7 @@
       <c r="AV55" s="16"/>
       <c r="AW55" s="17"/>
     </row>
-    <row r="56" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="30"/>
       <c r="C56" s="37"/>
       <c r="D56" s="42">
@@ -10110,7 +10110,7 @@
       <c r="AV56" s="16"/>
       <c r="AW56" s="17"/>
     </row>
-    <row r="57" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="30"/>
       <c r="C57" s="37"/>
       <c r="D57" s="82">
@@ -10172,7 +10172,7 @@
       <c r="AV57" s="16"/>
       <c r="AW57" s="17"/>
     </row>
-    <row r="58" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="30"/>
       <c r="C58" s="37"/>
       <c r="D58" s="42">
@@ -10234,7 +10234,7 @@
       <c r="AV58" s="16"/>
       <c r="AW58" s="17"/>
     </row>
-    <row r="59" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B59" s="30"/>
       <c r="C59" s="37"/>
       <c r="D59" s="42">
@@ -10296,7 +10296,7 @@
       <c r="AV59" s="16"/>
       <c r="AW59" s="17"/>
     </row>
-    <row r="60" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" s="30"/>
       <c r="C60" s="37"/>
       <c r="D60" s="42">
@@ -10358,7 +10358,7 @@
       <c r="AV60" s="16"/>
       <c r="AW60" s="17"/>
     </row>
-    <row r="61" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B61" s="30"/>
       <c r="C61" s="37"/>
       <c r="D61" s="42">
@@ -10420,7 +10420,7 @@
       <c r="AV61" s="16"/>
       <c r="AW61" s="17"/>
     </row>
-    <row r="62" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B62" s="30"/>
       <c r="C62" s="37"/>
       <c r="D62" s="42">
@@ -10482,7 +10482,7 @@
       <c r="AV62" s="16"/>
       <c r="AW62" s="17"/>
     </row>
-    <row r="63" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B63" s="30"/>
       <c r="C63" s="37"/>
       <c r="D63" s="42">
@@ -10544,7 +10544,7 @@
       <c r="AV63" s="16"/>
       <c r="AW63" s="17"/>
     </row>
-    <row r="64" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B64" s="30"/>
       <c r="C64" s="37"/>
       <c r="D64" s="42">
@@ -10583,7 +10583,7 @@
         <v>127</v>
       </c>
       <c r="AC64" s="40"/>
-      <c r="AD64" s="10" t="s">
+      <c r="AD64" s="19" t="s">
         <v>131</v>
       </c>
       <c r="AE64" s="16"/>
@@ -10606,7 +10606,7 @@
       <c r="AV64" s="16"/>
       <c r="AW64" s="17"/>
     </row>
-    <row r="65" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="30"/>
       <c r="C65" s="37"/>
       <c r="D65" s="42">
@@ -10664,7 +10664,7 @@
       <c r="AV65" s="16"/>
       <c r="AW65" s="17"/>
     </row>
-    <row r="66" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="30"/>
       <c r="C66" s="37"/>
       <c r="D66" s="42">
@@ -10722,7 +10722,7 @@
       <c r="AV66" s="16"/>
       <c r="AW66" s="17"/>
     </row>
-    <row r="67" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B67" s="29"/>
       <c r="C67" s="33"/>
       <c r="D67" s="42">
@@ -10780,8 +10780,8 @@
       <c r="AV67" s="16"/>
       <c r="AW67" s="17"/>
     </row>
-    <row r="68" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="69" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="68" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="69" spans="2:49" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
